--- a/site/downloads/ranch-expense-ledger.xlsx
+++ b/site/downloads/ranch-expense-ledger.xlsx
@@ -563,7 +563,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Built by Lone Star Exotics Hub (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
+          <t>Built by Exotic Ranch &amp; Wildlife Network (draft), Oct 2026. Verify every figure against the current publication; tax law changes.</t>
         </is>
       </c>
     </row>
@@ -1062,8 +1062,6 @@
           <t>No</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
